--- a/results/gmac_snr6dB/gmac_snr6dB_classA_Ru46_Rv23_SC/classA_Ru46_Rv23_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classA_Ru46_Rv23_SC/classA_Ru46_Rv23_snr6dB_SC.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +30,32 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +63,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,282 +457,280 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Gaussian MAC — Class A, (Ru=0.46, Rv=0.23), SNR=6dB, SC (L=1)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Symmetric capacity: Rx=Ry ≤ 0.6882 bits/use | Sum capacity: 1.3764 bits/use | Path: 0^(3N/8) 1^N 0^(5N/8)</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>ku</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>kv</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Ru</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Rv</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Sum Rate</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>BLER</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Codewords</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.0356</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="4" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.4375</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="5" t="n">
         <v>0.6875</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.0238</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="4" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.4688</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.2188</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.6876</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="6" t="n">
         <v>0.0058</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="4" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="5" t="n">
         <v>0.4531</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.2344</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.6875</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>0.004</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="4" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="5" t="n">
         <v>0.4531</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="5" t="n">
         <v>0.2344</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="5" t="n">
         <v>0.6875</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="6" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.002533</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>512</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>233</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>0.0002</v>
       </c>
-      <c r="H9" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>256</v>
-      </c>
-      <c r="B10" t="n">
-        <v>117</v>
-      </c>
-      <c r="C10" t="n">
-        <v>59</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>512</v>
-      </c>
-      <c r="B11" t="n">
-        <v>233</v>
-      </c>
-      <c r="C11" t="n">
-        <v>119</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.4551</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="H11" s="4" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>467</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>0.2324</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1024</v>
-      </c>
-      <c r="B12" t="n">
-        <v>467</v>
-      </c>
-      <c r="C12" t="n">
-        <v>238</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4561</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2324</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="F12" s="5" t="n">
         <v>0.6885</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="G12" s="6" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>8000</v>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -703,16 +738,20 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.688195269487774</v>
+        <v>0.6882</v>
       </c>
       <c r="E14" t="n">
-        <v>0.688195269487774</v>
+        <v>0.6882</v>
       </c>
       <c r="F14" t="n">
-        <v>1.376390538975548</v>
+        <v>1.3764</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>